--- a/public/sample-sheet.xlsx
+++ b/public/sample-sheet.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFE3B557C8bE698B4597Ee505F7Ee482cFdCDF588</t>
+          <t>0xfE3b557C8be698b4597eE505F7Ee482CFdcDf588</t>
         </is>
       </c>
       <c r="C5" t="n">
